--- a/data/trans_dic/IP16A98-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A98-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos</t>
+          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,49</t>
+          <t>0,0; 20,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,62; 44,85</t>
+          <t>7,42; 42,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,22; 63,6</t>
+          <t>8,6; 64,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,56; 40,82</t>
+          <t>8,55; 42,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 26,59</t>
+          <t>2,93; 28,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,75; 31,87</t>
+          <t>7,81; 34,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 26,45</t>
+          <t>5,47; 25,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 26,31</t>
+          <t>7,47; 29,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,02; 49,08</t>
+          <t>11,61; 47,75</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 25,93</t>
+          <t>2,94; 24,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 25,75</t>
+          <t>2,43; 24,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 24,73</t>
+          <t>2,25; 25,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 24,87</t>
+          <t>2,62; 23,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 25,43</t>
+          <t>3,0; 25,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 18,78</t>
+          <t>3,86; 19,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,36; 20,27</t>
+          <t>5,51; 19,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 20,2</t>
+          <t>4,7; 19,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,17; 18,08</t>
+          <t>4,48; 17,69</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 36,0</t>
+          <t>4,49; 35,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,69; 54,79</t>
+          <t>0,0; 54,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,13; 36,06</t>
+          <t>6,01; 35,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 26,17</t>
+          <t>2,98; 25,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,64</t>
+          <t>0,0; 50,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,25; 46,92</t>
+          <t>11,4; 45,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 24,31</t>
+          <t>5,53; 23,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,12; 40,98</t>
+          <t>8,29; 40,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,1; 36,08</t>
+          <t>12,66; 37,82</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,26</t>
+          <t>0,0; 21,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,23; 45,03</t>
+          <t>14,18; 44,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,46; 50,51</t>
+          <t>8,23; 51,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 38,42</t>
+          <t>4,68; 37,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,13; 48,83</t>
+          <t>16,71; 48,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,8</t>
+          <t>0,0; 52,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 24,69</t>
+          <t>5,36; 22,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,48; 41,37</t>
+          <t>19,13; 41,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,15; 40,5</t>
+          <t>9,27; 39,55</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,12</t>
+          <t>0,0; 24,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,4</t>
+          <t>0,0; 47,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 46,23</t>
+          <t>5,31; 44,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,15</t>
+          <t>0,0; 29,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,97</t>
+          <t>0,0; 64,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,8; 61,34</t>
+          <t>5,98; 60,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,57</t>
+          <t>0,0; 16,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 40,73</t>
+          <t>5,12; 42,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,16; 45,88</t>
+          <t>9,34; 45,19</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,87; 53,62</t>
+          <t>7,06; 53,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,46</t>
+          <t>0,0; 42,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,44</t>
+          <t>0,0; 35,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,7; 29,25</t>
+          <t>3,78; 33,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,27; 75,08</t>
+          <t>17,33; 74,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,73; 43,31</t>
+          <t>7,61; 41,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,49; 33,08</t>
+          <t>7,99; 32,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,65; 47,91</t>
+          <t>12,82; 49,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,32; 30,4</t>
+          <t>5,83; 30,03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,43; 20,63</t>
+          <t>2,46; 21,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,67; 34,18</t>
+          <t>4,03; 32,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,1; 29,9</t>
+          <t>6,72; 29,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 30,65</t>
+          <t>5,37; 28,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,23</t>
+          <t>0,0; 35,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,28; 43,77</t>
+          <t>9,23; 45,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,1; 20,33</t>
+          <t>5,26; 21,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 21,87</t>
+          <t>2,42; 22,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,67; 34,04</t>
+          <t>11,27; 34,84</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,2; 40,17</t>
+          <t>9,69; 40,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,02; 25,75</t>
+          <t>3,14; 27,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,38; 69,08</t>
+          <t>17,24; 69,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,1; 44,62</t>
+          <t>11,86; 45,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,68; 37,21</t>
+          <t>12,54; 38,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,73; 45,57</t>
+          <t>6,33; 48,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,23; 36,25</t>
+          <t>13,94; 36,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,06; 27,92</t>
+          <t>10,71; 27,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,89; 48,58</t>
+          <t>12,92; 47,58</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,16; 16,92</t>
+          <t>8,11; 16,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,59; 22,82</t>
+          <t>12,32; 23,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,46; 27,41</t>
+          <t>11,06; 28,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,93; 20,32</t>
+          <t>10,71; 20,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,75; 26,83</t>
+          <t>14,86; 27,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,19; 25,16</t>
+          <t>13,53; 25,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,65; 17,31</t>
+          <t>10,81; 17,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,93; 22,79</t>
+          <t>14,85; 22,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,66; 24,32</t>
+          <t>13,02; 23,65</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3446</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8679</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3871</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3959</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4464</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>5445</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>12639</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3175</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1194; 6791</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2612; 19602</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1542; 7627</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>563; 5477</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1743; 7597</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1841; 8593</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2637; 10384</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>6120; 25165</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2623</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3026</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7561</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2523</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4599</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5146</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>12159</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>672; 5707</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>662; 6703</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1421; 15912</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>622; 5653</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>621; 5271</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1861; 9327</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2568; 9241</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2256; 9269</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4982; 19679</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2710</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2246</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3159</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2136</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5421</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4847</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3698</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>8580</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>698; 5584</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5142</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1077; 6387</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>645; 5458</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4232</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2314; 9301</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2052; 8740</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1481; 7262</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4838; 14457</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1277</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6677</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3094</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8084</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1809</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4050</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>14761</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4903</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3994</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3374; 10612</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1031; 6423</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>713; 5668</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>4274; 12406</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5856</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1818; 7771</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>9446; 20441</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2186; 9331</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1599</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1228</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2835</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>4434</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3339</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3108</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>438; 3692</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3476</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3332</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>639; 6439</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4102</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>598; 5019</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1768; 8553</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3822</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5167</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>5071</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>3245</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>775; 5930</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3902</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2700</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>685; 5980</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1505; 6478</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1036; 5609</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2323; 9461</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2280; 8794</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1241; 6392</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1849</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>4729</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>3904</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>9706</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>5961</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2563</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>14436</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>654; 5648</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>574; 4638</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2003; 8913</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1361; 7276</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3763</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4094; 20097</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2729; 10939</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>602; 5505</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>8359; 25832</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>4549</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3411</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5435</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>5805</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2452</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>9984</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>8209</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>5863</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1998; 8273</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>658; 5733</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1399; 5626</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2481; 9551</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>3138; 9635</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>741; 5697</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>5790; 15205</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>4918; 12706</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>2560; 9430</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>21668</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>32743</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>23475</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>33516</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>40948</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>46712</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>66259</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>11723; 24369</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>15703; 29345</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>19656; 49918</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>16546; 31573</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>18317; 33834</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>24660; 45555</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>32332; 51727</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>37240; 56783</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>46865; 85107</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A98-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A98-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,34</t>
+          <t>0,0; 20,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,42; 42,2</t>
+          <t>8,13; 43,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,6; 64,51</t>
+          <t>8,12; 67,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,55; 42,32</t>
+          <t>7,6; 41,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 28,51</t>
+          <t>2,95; 24,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 34,03</t>
+          <t>7,8; 32,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 25,55</t>
+          <t>4,86; 26,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 29,42</t>
+          <t>7,67; 26,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,61; 47,75</t>
+          <t>11,37; 50,35</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 24,99</t>
+          <t>2,91; 25,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 24,59</t>
+          <t>2,41; 26,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 25,24</t>
+          <t>1,85; 25,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 23,81</t>
+          <t>2,66; 24,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 25,49</t>
+          <t>3,04; 27,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 19,36</t>
+          <t>4,32; 18,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,51; 19,84</t>
+          <t>5,23; 20,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,7; 19,33</t>
+          <t>4,25; 20,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 17,69</t>
+          <t>4,78; 17,7</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 35,95</t>
+          <t>4,45; 39,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,0</t>
+          <t>7,72; 54,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,01; 35,6</t>
+          <t>6,36; 37,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 25,26</t>
+          <t>2,91; 24,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,75</t>
+          <t>0,0; 51,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,4; 45,85</t>
+          <t>11,93; 46,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 23,53</t>
+          <t>5,53; 23,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,29; 40,66</t>
+          <t>8,27; 40,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,66; 37,82</t>
+          <t>12,25; 34,59</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,38</t>
+          <t>0,0; 21,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,18; 44,59</t>
+          <t>15,35; 45,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,23; 51,29</t>
+          <t>7,54; 51,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 37,18</t>
+          <t>4,58; 38,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,71; 48,5</t>
+          <t>17,96; 49,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,89</t>
+          <t>0,0; 47,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 22,91</t>
+          <t>4,14; 22,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,13; 41,4</t>
+          <t>20,09; 41,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,27; 39,55</t>
+          <t>8,83; 38,36</t>
         </is>
       </c>
     </row>
@@ -1118,32 +1118,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,2</t>
+          <t>0,0; 20,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,74</t>
+          <t>0,0; 49,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,31; 44,82</t>
+          <t>5,54; 47,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,99</t>
+          <t>0,0; 24,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,48</t>
+          <t>0,0; 63,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,98; 60,24</t>
+          <t>6,11; 59,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,12; 42,97</t>
+          <t>5,13; 42,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,34; 45,19</t>
+          <t>9,47; 48,05</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,06; 53,97</t>
+          <t>7,24; 53,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,86</t>
+          <t>0,0; 40,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,16</t>
+          <t>0,0; 35,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,78; 33,05</t>
+          <t>3,75; 28,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,33; 74,59</t>
+          <t>16,14; 74,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,61; 41,22</t>
+          <t>7,25; 41,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,99; 32,53</t>
+          <t>7,76; 32,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,82; 49,43</t>
+          <t>12,62; 48,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,83; 30,03</t>
+          <t>5,91; 30,47</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 21,27</t>
+          <t>2,46; 20,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,03; 32,55</t>
+          <t>3,71; 33,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,72; 29,92</t>
+          <t>6,94; 29,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,37; 28,71</t>
+          <t>7,27; 31,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,49</t>
+          <t>0,0; 33,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,23; 45,31</t>
+          <t>10,08; 45,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,26; 21,07</t>
+          <t>5,21; 20,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,42; 22,15</t>
+          <t>2,45; 24,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,27; 34,84</t>
+          <t>11,13; 35,34</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,69; 40,13</t>
+          <t>9,41; 38,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,14; 27,41</t>
+          <t>2,9; 27,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,24; 69,35</t>
+          <t>15,18; 71,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,86; 45,67</t>
+          <t>11,33; 46,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,54; 38,52</t>
+          <t>12,39; 39,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,33; 48,66</t>
+          <t>5,72; 49,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,94; 36,61</t>
+          <t>14,66; 36,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,71; 27,66</t>
+          <t>11,15; 28,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,92; 47,58</t>
+          <t>14,93; 50,05</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,11; 16,85</t>
+          <t>8,16; 17,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,32; 23,02</t>
+          <t>11,96; 23,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,06; 28,09</t>
+          <t>11,04; 27,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,71; 20,43</t>
+          <t>10,67; 20,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,86; 27,45</t>
+          <t>15,43; 27,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,53; 25,0</t>
+          <t>13,15; 25,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,81; 17,29</t>
+          <t>10,55; 17,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,85; 22,65</t>
+          <t>15,13; 23,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,02; 23,65</t>
+          <t>13,77; 23,99</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3175</t>
+          <t>0; 3167</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1194; 6791</t>
+          <t>1308; 6995</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2612; 19602</t>
+          <t>2467; 20566</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1542; 7627</t>
+          <t>1369; 7502</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>563; 5477</t>
+          <t>567; 4706</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1743; 7597</t>
+          <t>1740; 7311</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1841; 8593</t>
+          <t>1634; 9028</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2637; 10384</t>
+          <t>2708; 9484</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6120; 25165</t>
+          <t>5993; 26538</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>672; 5707</t>
+          <t>664; 5865</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>662; 6703</t>
+          <t>657; 7277</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1421; 15912</t>
+          <t>1166; 15933</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>622; 5653</t>
+          <t>631; 5787</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>621; 5271</t>
+          <t>629; 5608</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1861; 9327</t>
+          <t>2081; 9027</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2568; 9241</t>
+          <t>2435; 9359</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2256; 9269</t>
+          <t>2036; 9737</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4982; 19679</t>
+          <t>5313; 19690</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>698; 5584</t>
+          <t>691; 6071</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5142</t>
+          <t>735; 5187</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1077; 6387</t>
+          <t>1142; 6674</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645; 5458</t>
+          <t>628; 5221</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4232</t>
+          <t>0; 4257</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2314; 9301</t>
+          <t>2421; 9485</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2052; 8740</t>
+          <t>2052; 8713</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1481; 7262</t>
+          <t>1476; 7320</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4838; 14457</t>
+          <t>4683; 13222</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3994</t>
+          <t>0; 4024</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3374; 10612</t>
+          <t>3653; 10933</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1031; 6423</t>
+          <t>944; 6395</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>713; 5668</t>
+          <t>698; 5908</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4274; 12406</t>
+          <t>4595; 12620</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5856</t>
+          <t>0; 5242</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1818; 7771</t>
+          <t>1403; 7760</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9446; 20441</t>
+          <t>9919; 20426</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2186; 9331</t>
+          <t>2084; 9050</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3339</t>
+          <t>0; 2787</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3108</t>
+          <t>0; 3192</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>438; 3692</t>
+          <t>456; 3874</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3476</t>
+          <t>0; 2815</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3332</t>
+          <t>0; 3299</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>639; 6439</t>
+          <t>654; 6348</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4102</t>
+          <t>0; 4101</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>598; 5019</t>
+          <t>599; 4906</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1768; 8553</t>
+          <t>1793; 9094</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>775; 5930</t>
+          <t>795; 5931</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3902</t>
+          <t>0; 3689</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2700</t>
+          <t>0; 2740</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>685; 5980</t>
+          <t>678; 5107</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1505; 6478</t>
+          <t>1402; 6471</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1036; 5609</t>
+          <t>986; 5626</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2323; 9461</t>
+          <t>2258; 9388</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2280; 8794</t>
+          <t>2246; 8671</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1241; 6392</t>
+          <t>1259; 6487</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>654; 5648</t>
+          <t>654; 5342</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>574; 4638</t>
+          <t>529; 4817</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2003; 8913</t>
+          <t>2066; 8846</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1361; 7276</t>
+          <t>1841; 7919</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3763</t>
+          <t>0; 3578</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4094; 20097</t>
+          <t>4469; 20051</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2729; 10939</t>
+          <t>2703; 10834</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>602; 5505</t>
+          <t>608; 6057</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8359; 25832</t>
+          <t>8252; 26201</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1998; 8273</t>
+          <t>1941; 7915</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>658; 5733</t>
+          <t>607; 5774</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1399; 5626</t>
+          <t>1232; 5781</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2481; 9551</t>
+          <t>2370; 9664</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3138; 9635</t>
+          <t>3100; 9797</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>741; 5697</t>
+          <t>670; 5750</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5790; 15205</t>
+          <t>6090; 15137</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4918; 12706</t>
+          <t>5123; 12869</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2560; 9430</t>
+          <t>2960; 9920</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>11723; 24369</t>
+          <t>11808; 24872</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15703; 29345</t>
+          <t>15240; 29441</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19656; 49918</t>
+          <t>19615; 49092</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16546; 31573</t>
+          <t>16488; 31501</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>18317; 33834</t>
+          <t>19022; 33523</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24660; 45555</t>
+          <t>23963; 46435</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32332; 51727</t>
+          <t>31577; 51700</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>37240; 56783</t>
+          <t>37927; 58056</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>46865; 85107</t>
+          <t>49549; 86352</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A98-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A98-Provincia-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
+          <t>Menores que consumieron otros medicamentos (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21,47%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10,41%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18,63%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,8%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>21,41%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28,57%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21,47%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,41%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,29</t>
+          <t>8,56; 40,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,13; 43,47</t>
+          <t>2,83; 26,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,12; 67,69</t>
+          <t>8,23; 33,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 41,62</t>
+          <t>0,0; 20,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 24,5</t>
+          <t>7,62; 44,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,8; 32,75</t>
+          <t>6,08; 31,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 26,84</t>
+          <t>4,85; 26,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,67; 26,87</t>
+          <t>7,26; 26,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,37; 50,35</t>
+          <t>10,2; 28,24</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,63%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>11,49%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>11,1%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 25,68</t>
+          <t>2,6; 24,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 26,69</t>
+          <t>2,96; 25,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 25,27</t>
+          <t>4,03; 19,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 24,37</t>
+          <t>2,83; 25,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 27,11</t>
+          <t>2,41; 25,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 18,74</t>
+          <t>9,53; 33,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,23; 20,09</t>
+          <t>5,36; 20,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 20,31</t>
+          <t>4,73; 20,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 17,7</t>
+          <t>8,36; 21,02</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,89%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17,42%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23,68%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>17,45%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>23,58%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17,61%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,89%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,45; 39,09</t>
+          <t>2,96; 26,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,72; 54,47</t>
+          <t>0,0; 51,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 37,2</t>
+          <t>9,36; 42,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 24,16</t>
+          <t>4,35; 36,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,05</t>
+          <t>7,69; 54,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,93; 46,76</t>
+          <t>6,13; 33,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 23,46</t>
+          <t>5,6; 24,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,27; 40,98</t>
+          <t>8,12; 40,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,25; 34,59</t>
+          <t>10,93; 32,31</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18,19%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31,6%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16,3%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>6,84%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>28,06%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>24,71%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>31,6%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,54</t>
+          <t>4,45; 38,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,35; 45,94</t>
+          <t>18,13; 48,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 51,07</t>
+          <t>0,0; 50,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 38,76</t>
+          <t>0,0; 24,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,96; 49,34</t>
+          <t>14,23; 45,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,34</t>
+          <t>9,35; 51,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 22,87</t>
+          <t>4,29; 24,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,09; 41,37</t>
+          <t>20,48; 41,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,83; 38,36</t>
+          <t>9,65; 42,77</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23,77%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>29,69%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,78%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>11,84%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19,41%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>23,77%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,2</t>
+          <t>0,0; 25,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,03</t>
+          <t>0,0; 63,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,54; 47,04</t>
+          <t>6,71; 65,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,29</t>
+          <t>0,0; 30,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,83</t>
+          <t>0,0; 47,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,11; 59,39</t>
+          <t>6,44; 48,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,16</t>
+          <t>0,0; 15,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,13; 42,01</t>
+          <t>5,03; 40,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,47; 48,05</t>
+          <t>9,95; 48,13</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11,95%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>44,01%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19,81%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>27,34%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>13,72%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11,95%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>44,01%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,24; 53,97</t>
+          <t>3,7; 29,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,52</t>
+          <t>17,27; 75,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,68</t>
+          <t>7,22; 44,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,75; 28,22</t>
+          <t>6,87; 53,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,14; 74,51</t>
+          <t>0,0; 37,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,25; 41,35</t>
+          <t>0,0; 38,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,76; 32,28</t>
+          <t>7,49; 33,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,62; 48,74</t>
+          <t>12,65; 47,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,91; 30,47</t>
+          <t>5,94; 29,97</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15,4%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>22,0%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>7,75%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>12,98%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15,88%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,73%</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 20,11</t>
+          <t>5,31; 30,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,71; 33,8</t>
+          <t>0,0; 31,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,94; 29,7</t>
+          <t>8,44; 44,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,27; 31,25</t>
+          <t>2,43; 20,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,74</t>
+          <t>3,67; 34,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,08; 45,21</t>
+          <t>7,19; 30,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,21; 20,87</t>
+          <t>5,1; 20,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 24,37</t>
+          <t>4,33; 21,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,13; 35,34</t>
+          <t>10,78; 35,14</t>
         </is>
       </c>
     </row>
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>25,99%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>23,21%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>21,61%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>22,07%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>11,49%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>42,05%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>25,99%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>23,21%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,41; 38,39</t>
+          <t>11,1; 44,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,9; 27,6</t>
+          <t>10,68; 37,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,18; 71,26</t>
+          <t>5,43; 45,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,33; 46,21</t>
+          <t>9,2; 40,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,39; 39,17</t>
+          <t>3,02; 25,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,72; 49,11</t>
+          <t>14,46; 72,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,66; 36,45</t>
+          <t>14,23; 36,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,15; 28,02</t>
+          <t>10,06; 27,92</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,93; 50,05</t>
+          <t>14,51; 52,4</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>18,36%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>12,08%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>17,0%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>18,42%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>15,19%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,16; 17,2</t>
+          <t>10,93; 20,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,96; 23,1</t>
+          <t>14,75; 26,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,04; 27,62</t>
+          <t>13,24; 25,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,67; 20,38</t>
+          <t>8,16; 16,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,43; 27,19</t>
+          <t>11,59; 22,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,15; 25,49</t>
+          <t>14,25; 24,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,55; 17,28</t>
+          <t>10,65; 17,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,13; 23,15</t>
+          <t>14,93; 22,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,77; 23,99</t>
+          <t>15,03; 23,36</t>
         </is>
       </c>
     </row>
@@ -1654,20 +1654,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
+          <t>Menores que consumieron otros medicamentos (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,32 +1755,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3871</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3591</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>594</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>3446</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8679</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3871</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>7076</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3167</t>
+          <t>1543; 7357</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1308; 6995</t>
+          <t>544; 5106</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2467; 20566</t>
+          <t>1586; 6394</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1369; 7502</t>
+          <t>0; 3200</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>567; 4706</t>
+          <t>1226; 7217</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1740; 7311</t>
+          <t>1264; 6536</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1634; 9028</t>
+          <t>1630; 8896</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2708; 9484</t>
+          <t>2561; 9286</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5993; 26538</t>
+          <t>4088; 11315</t>
         </is>
       </c>
     </row>
@@ -1923,27 +1923,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2523</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3883</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2623</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3026</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7561</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2523</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1939</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12159</t>
+          <t>11414</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>664; 5865</t>
+          <t>618; 5903</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>657; 7277</t>
+          <t>613; 5258</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1166; 15933</t>
+          <t>1719; 8225</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>631; 5787</t>
+          <t>645; 5923</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>629; 5608</t>
+          <t>657; 7021</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2081; 9027</t>
+          <t>3693; 12894</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2435; 9359</t>
+          <t>2495; 9442</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2036; 9737</t>
+          <t>2269; 9685</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5313; 19690</t>
+          <t>6806; 17121</t>
         </is>
       </c>
     </row>
@@ -2081,32 +2081,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2136</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4186</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>2710</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2246</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3159</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2136</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1452</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8580</t>
+          <t>6998</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>691; 6071</t>
+          <t>640; 5654</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>735; 5187</t>
+          <t>0; 4306</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1142; 6674</t>
+          <t>1656; 7524</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>628; 5221</t>
+          <t>676; 5591</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4257</t>
+          <t>732; 5218</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2421; 9485</t>
+          <t>1054; 5681</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2052; 8713</t>
+          <t>2080; 9027</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1476; 7320</t>
+          <t>1450; 7320</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4683; 13222</t>
+          <t>3814; 11267</t>
         </is>
       </c>
     </row>
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8084</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1698</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1277</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>6677</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3094</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8084</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4964</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4024</t>
+          <t>678; 5855</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3653; 10933</t>
+          <t>4637; 12490</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>944; 6395</t>
+          <t>0; 5211</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>698; 5908</t>
+          <t>0; 4533</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4595; 12620</t>
+          <t>3386; 10718</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5242</t>
+          <t>1142; 6253</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1403; 7760</t>
+          <t>1454; 8377</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9919; 20426</t>
+          <t>10115; 20428</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2084; 9050</t>
+          <t>2184; 9682</t>
         </is>
       </c>
     </row>
@@ -2412,22 +2412,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2460,32 +2460,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1228</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>659</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>771</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1228</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4638</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2787</t>
+          <t>0; 2915</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3192</t>
+          <t>0; 3306</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>456; 3874</t>
+          <t>654; 6397</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2815</t>
+          <t>0; 4154</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3299</t>
+          <t>0; 3086</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>654; 6348</t>
+          <t>544; 4135</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4101</t>
+          <t>0; 3953</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>599; 4906</t>
+          <t>588; 4757</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1793; 9094</t>
+          <t>1808; 8749</t>
         </is>
       </c>
     </row>
@@ -2570,32 +2570,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3822</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2266</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>3004</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1249</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2163</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3822</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2734</t>
+          <t>582</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>2848</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>795; 5931</t>
+          <t>669; 5292</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3689</t>
+          <t>1500; 6521</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2740</t>
+          <t>826; 5110</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>678; 5107</t>
+          <t>755; 5892</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1402; 6471</t>
+          <t>0; 3411</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>986; 5626</t>
+          <t>0; 2980</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2258; 9388</t>
+          <t>2177; 9619</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2246; 8671</t>
+          <t>2250; 8523</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1259; 6487</t>
+          <t>1134; 5724</t>
         </is>
       </c>
     </row>
@@ -2733,27 +2733,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>3904</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>9247</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>2057</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1849</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>4729</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>3904</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>14093</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>654; 5342</t>
+          <t>1345; 7769</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>529; 4817</t>
+          <t>0; 3311</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2066; 8846</t>
+          <t>3547; 18771</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1841; 7919</t>
+          <t>646; 5479</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3578</t>
+          <t>523; 4871</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4469; 20051</t>
+          <t>2176; 9206</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2703; 10834</t>
+          <t>2647; 10552</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>608; 6057</t>
+          <t>1077; 5435</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8252; 26201</t>
+          <t>7795; 25405</t>
         </is>
       </c>
     </row>
@@ -2901,27 +2901,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>5435</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>5805</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2530</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>4549</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2403</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>3411</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5435</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>5805</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>6074</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1941; 7915</t>
+          <t>2322; 9332</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>607; 5774</t>
+          <t>2672; 9307</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1232; 5781</t>
+          <t>636; 5365</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2370; 9664</t>
+          <t>1896; 8281</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3100; 9797</t>
+          <t>631; 5387</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>670; 5750</t>
+          <t>1104; 5566</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6090; 15137</t>
+          <t>5911; 15054</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5123; 12869</t>
+          <t>4621; 12823</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2960; 9920</t>
+          <t>2806; 10134</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>23475</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>30293</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>17473</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>21668</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>32743</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>23475</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>25045</t>
-        </is>
-      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33516</t>
+          <t>27812</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>58105</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>11808; 24872</t>
+          <t>16896; 31398</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15240; 29441</t>
+          <t>18186; 33081</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19615; 49092</t>
+          <t>21832; 42758</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16488; 31501</t>
+          <t>11807; 24464</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>19022; 33523</t>
+          <t>14773; 29092</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23963; 46435</t>
+          <t>20372; 35456</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31577; 51700</t>
+          <t>31850; 51779</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>37927; 58056</t>
+          <t>37429; 57146</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>49549; 86352</t>
+          <t>46288; 71920</t>
         </is>
       </c>
     </row>
